--- a/docs/naver_체험단候補リスト_202607.xlsx
+++ b/docs/naver_체험단候補リスト_202607.xlsx
@@ -1347,7 +1347,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>■ 条件の上限: 原稿料は1本50만원まで（Aランクのみ）。提供は9〜10月平日2泊・週末在庫は使わない。</t>
+          <t>■ 条件の上限: 原稿料は1本50만원まで（Aランクのみ）。提供は9〜10月平日1〜2泊（2泊推奨）・週末在庫は使わない。</t>
         </is>
       </c>
     </row>
@@ -1358,6 +1358,7 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
